--- a/cuerpos_celestes.xlsx
+++ b/cuerpos_celestes.xlsx
@@ -1,40 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/193cefc03e0993e2/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usuario\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{12D0F6B4-E37F-4943-ADD7-B85509F0C9CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07AFA493-A08D-412B-B894-E222CC52903D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6A79693E-CD20-4927-898B-223E9D7D5B8D}"/>
+    <workbookView xWindow="3255" yWindow="2310" windowWidth="15375" windowHeight="7830" xr2:uid="{6A79693E-CD20-4927-898B-223E9D7D5B8D}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="154">
   <si>
     <t>nombre</t>
   </si>
@@ -60,10 +51,442 @@
     <t>Sistema Solar</t>
   </si>
   <si>
-    <t>Sol</t>
-  </si>
-  <si>
     <t>Estrella</t>
+  </si>
+  <si>
+    <t>Mercurio</t>
+  </si>
+  <si>
+    <t>Venus</t>
+  </si>
+  <si>
+    <t>Marte</t>
+  </si>
+  <si>
+    <t>Jupiter</t>
+  </si>
+  <si>
+    <t>Saturno</t>
+  </si>
+  <si>
+    <t>Urano</t>
+  </si>
+  <si>
+    <t>Neptuno</t>
+  </si>
+  <si>
+    <t>Luna</t>
+  </si>
+  <si>
+    <t>Satelite</t>
+  </si>
+  <si>
+    <t>Sistema Tierra-Luna</t>
+  </si>
+  <si>
+    <t>Europa</t>
+  </si>
+  <si>
+    <t>Ganímedes</t>
+  </si>
+  <si>
+    <t>Io</t>
+  </si>
+  <si>
+    <t>Calisto</t>
+  </si>
+  <si>
+    <t>Titan</t>
+  </si>
+  <si>
+    <t>Encelado</t>
+  </si>
+  <si>
+    <t>Mimas</t>
+  </si>
+  <si>
+    <t>Fobos</t>
+  </si>
+  <si>
+    <t>Deimos</t>
+  </si>
+  <si>
+    <t>Pluton</t>
+  </si>
+  <si>
+    <t>Planeta Enano</t>
+  </si>
+  <si>
+    <t>Cinturon de Kuiper</t>
+  </si>
+  <si>
+    <t>Eris</t>
+  </si>
+  <si>
+    <t>Cinturon Disperso</t>
+  </si>
+  <si>
+    <t>Haumea</t>
+  </si>
+  <si>
+    <t>Makemake</t>
+  </si>
+  <si>
+    <t>Ceres</t>
+  </si>
+  <si>
+    <t>Cinturon de Asteroides</t>
+  </si>
+  <si>
+    <t>Vesta</t>
+  </si>
+  <si>
+    <t>Asteroide</t>
+  </si>
+  <si>
+    <t>Pallas</t>
+  </si>
+  <si>
+    <t>Hygiea</t>
+  </si>
+  <si>
+    <t>Betelgeuse</t>
+  </si>
+  <si>
+    <t>Orión</t>
+  </si>
+  <si>
+    <t>Rigel</t>
+  </si>
+  <si>
+    <t>Sirio</t>
+  </si>
+  <si>
+    <t>Can Mayor</t>
+  </si>
+  <si>
+    <t>Proxima Centauri</t>
+  </si>
+  <si>
+    <t>Centauro</t>
+  </si>
+  <si>
+    <t>Alpha Centauri A</t>
+  </si>
+  <si>
+    <t>Alpha Centauri B</t>
+  </si>
+  <si>
+    <t>Vega</t>
+  </si>
+  <si>
+    <t>Lyra</t>
+  </si>
+  <si>
+    <t>Altair</t>
+  </si>
+  <si>
+    <t>Águila</t>
+  </si>
+  <si>
+    <t>Deneb</t>
+  </si>
+  <si>
+    <t>Cisne</t>
+  </si>
+  <si>
+    <t>Polaris</t>
+  </si>
+  <si>
+    <t>Osa Menor</t>
+  </si>
+  <si>
+    <t>Antares</t>
+  </si>
+  <si>
+    <t>Escorpio</t>
+  </si>
+  <si>
+    <t>Aldebaran</t>
+  </si>
+  <si>
+    <t>Tauro</t>
+  </si>
+  <si>
+    <t>Spica</t>
+  </si>
+  <si>
+    <t>Virgo</t>
+  </si>
+  <si>
+    <t>Arcturus</t>
+  </si>
+  <si>
+    <t>Boyero</t>
+  </si>
+  <si>
+    <t>Bellatrix</t>
+  </si>
+  <si>
+    <t>Capella</t>
+  </si>
+  <si>
+    <t>Auriga</t>
+  </si>
+  <si>
+    <t>Canopus</t>
+  </si>
+  <si>
+    <t>Carina</t>
+  </si>
+  <si>
+    <t>Archenar</t>
+  </si>
+  <si>
+    <t>Eridano</t>
+  </si>
+  <si>
+    <t>Mimosa</t>
+  </si>
+  <si>
+    <t>Cruz del sur</t>
+  </si>
+  <si>
+    <t>Alnilam</t>
+  </si>
+  <si>
+    <t>Alnitak</t>
+  </si>
+  <si>
+    <t>Saiph</t>
+  </si>
+  <si>
+    <t>Barnards star</t>
+  </si>
+  <si>
+    <t>Ofiuco</t>
+  </si>
+  <si>
+    <t>Trappist-1</t>
+  </si>
+  <si>
+    <t>Acuario</t>
+  </si>
+  <si>
+    <t>Keppler-22b</t>
+  </si>
+  <si>
+    <t>Keppler-452b</t>
+  </si>
+  <si>
+    <t>Exoplaneta</t>
+  </si>
+  <si>
+    <t>Pegaso</t>
+  </si>
+  <si>
+    <t>Hd 209458 b</t>
+  </si>
+  <si>
+    <t>51 pegasi b</t>
+  </si>
+  <si>
+    <t>wasp-12b</t>
+  </si>
+  <si>
+    <t>Andromeda 1</t>
+  </si>
+  <si>
+    <t>Galaxia</t>
+  </si>
+  <si>
+    <t>Grupo local</t>
+  </si>
+  <si>
+    <t>Via lactea</t>
+  </si>
+  <si>
+    <t>Triangulum</t>
+  </si>
+  <si>
+    <t>Messier 87</t>
+  </si>
+  <si>
+    <t>Sombrero</t>
+  </si>
+  <si>
+    <t>Whirlpool</t>
+  </si>
+  <si>
+    <t>Canes Venatici</t>
+  </si>
+  <si>
+    <t>NGC 1300</t>
+  </si>
+  <si>
+    <t>Messier 81</t>
+  </si>
+  <si>
+    <t>Messier 82</t>
+  </si>
+  <si>
+    <t>Osa Mayor</t>
+  </si>
+  <si>
+    <t>Large Magellanic Cloud</t>
+  </si>
+  <si>
+    <t>Small Magellanic Cloud</t>
+  </si>
+  <si>
+    <t>Grupo Local</t>
+  </si>
+  <si>
+    <t>Nebulosa de Orion</t>
+  </si>
+  <si>
+    <t>Nebulosa</t>
+  </si>
+  <si>
+    <t>Nebulosa Helix</t>
+  </si>
+  <si>
+    <t>Nebulosa Carina</t>
+  </si>
+  <si>
+    <t>Nebulosa Aguila</t>
+  </si>
+  <si>
+    <t>Nebulosa Laguna</t>
+  </si>
+  <si>
+    <t>Nebulosa Trifida</t>
+  </si>
+  <si>
+    <t>Nebulosa Roseta</t>
+  </si>
+  <si>
+    <t>Nebulosa Cangrejo</t>
+  </si>
+  <si>
+    <t>Nebulosa Ojo de Gato</t>
+  </si>
+  <si>
+    <t>Serpens</t>
+  </si>
+  <si>
+    <t>Sagitario</t>
+  </si>
+  <si>
+    <t>Monoceros</t>
+  </si>
+  <si>
+    <t>Dragon</t>
+  </si>
+  <si>
+    <t>Sagitario A</t>
+  </si>
+  <si>
+    <t>Agujero Negro</t>
+  </si>
+  <si>
+    <t>Centro Galáctico</t>
+  </si>
+  <si>
+    <t>TON 618</t>
+  </si>
+  <si>
+    <t>Cygnus X-1</t>
+  </si>
+  <si>
+    <t>V616 Monocerotis</t>
+  </si>
+  <si>
+    <t>Halley</t>
+  </si>
+  <si>
+    <t>Cometa</t>
+  </si>
+  <si>
+    <t>Sistema solar</t>
+  </si>
+  <si>
+    <t>Hale-Bopp</t>
+  </si>
+  <si>
+    <t>Hyakutake</t>
+  </si>
+  <si>
+    <t>Bennu</t>
+  </si>
+  <si>
+    <t>Apophis</t>
+  </si>
+  <si>
+    <t>Cercano a la Tierra</t>
+  </si>
+  <si>
+    <t>Eros</t>
+  </si>
+  <si>
+    <t>Itokawa</t>
+  </si>
+  <si>
+    <t>Ryugu</t>
+  </si>
+  <si>
+    <t>Charon</t>
+  </si>
+  <si>
+    <t>Triton</t>
+  </si>
+  <si>
+    <t>Oberon</t>
+  </si>
+  <si>
+    <t>Titania</t>
+  </si>
+  <si>
+    <t>Umbriel</t>
+  </si>
+  <si>
+    <t>Ariel</t>
+  </si>
+  <si>
+    <t>Miranda</t>
+  </si>
+  <si>
+    <t>Rhea</t>
+  </si>
+  <si>
+    <t>Dione</t>
+  </si>
+  <si>
+    <t>Tethys</t>
+  </si>
+  <si>
+    <t>Iapetus</t>
+  </si>
+  <si>
+    <t>Hyperion</t>
+  </si>
+  <si>
+    <t>Phoebe</t>
+  </si>
+  <si>
+    <t>Proteus</t>
+  </si>
+  <si>
+    <t>Nereid</t>
+  </si>
+  <si>
+    <t>Larissa</t>
+  </si>
+  <si>
+    <t>Despina</t>
+  </si>
+  <si>
+    <t>Galatea</t>
   </si>
 </sst>
 </file>
@@ -107,7 +530,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -115,6 +538,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -449,10 +873,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E31C2A1-38D5-48F2-B833-704BC7F1B31B}">
-  <dimension ref="A1:E3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:E106"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="4" max="4" width="17.42578125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -469,38 +896,1789 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>4879</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="2">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>12104</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B4" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C4" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="2">
-        <v>0</v>
-      </c>
-      <c r="E2" s="2">
+      <c r="D4" s="2">
+        <v>0</v>
+      </c>
+      <c r="E4">
         <v>12742</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="2">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>6779</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="2">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>139820</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="2">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>116460</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="2">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>50724</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" s="2">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>49244</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10" s="2">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>3474</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" s="2">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>3122</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" t="s">
+        <v>12</v>
+      </c>
+      <c r="D12" s="2">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>5268</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" t="s">
+        <v>12</v>
+      </c>
+      <c r="D13" s="2">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>3643</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" t="s">
+        <v>12</v>
+      </c>
+      <c r="D14" s="2">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>4821</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" t="s">
+        <v>13</v>
+      </c>
+      <c r="D15" s="2">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>5150</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>24</v>
+      </c>
+      <c r="B16" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" t="s">
+        <v>13</v>
+      </c>
+      <c r="D16" s="2">
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>25</v>
+      </c>
+      <c r="B17" t="s">
+        <v>17</v>
+      </c>
+      <c r="C17" t="s">
+        <v>13</v>
+      </c>
+      <c r="D17" s="2">
+        <v>0</v>
+      </c>
+      <c r="E17">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>26</v>
+      </c>
+      <c r="B18" t="s">
+        <v>17</v>
+      </c>
+      <c r="C18" t="s">
+        <v>11</v>
+      </c>
+      <c r="D18" s="2">
+        <v>0</v>
+      </c>
+      <c r="E18">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>27</v>
+      </c>
+      <c r="B19" t="s">
+        <v>17</v>
+      </c>
+      <c r="C19" t="s">
+        <v>11</v>
+      </c>
+      <c r="D19" s="2">
+        <v>0</v>
+      </c>
+      <c r="E19">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>28</v>
+      </c>
+      <c r="B20" t="s">
+        <v>29</v>
+      </c>
+      <c r="C20" t="s">
+        <v>30</v>
+      </c>
+      <c r="D20" s="2">
+        <v>0</v>
+      </c>
+      <c r="E20">
+        <v>2376</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>31</v>
+      </c>
+      <c r="B21" t="s">
+        <v>29</v>
+      </c>
+      <c r="C21" t="s">
+        <v>32</v>
+      </c>
+      <c r="D21" s="2">
+        <v>96</v>
+      </c>
+      <c r="E21">
+        <v>2326</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>33</v>
+      </c>
+      <c r="B22" t="s">
+        <v>29</v>
+      </c>
+      <c r="C22" t="s">
+        <v>30</v>
+      </c>
+      <c r="D22">
+        <v>50</v>
+      </c>
+      <c r="E22">
+        <v>1632</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>34</v>
+      </c>
+      <c r="B23" t="s">
+        <v>29</v>
+      </c>
+      <c r="C23" t="s">
+        <v>30</v>
+      </c>
+      <c r="D23" s="2">
+        <v>52</v>
+      </c>
+      <c r="E23">
+        <v>1430</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>35</v>
+      </c>
+      <c r="B24" t="s">
+        <v>29</v>
+      </c>
+      <c r="C24" t="s">
+        <v>36</v>
+      </c>
+      <c r="D24" s="2">
+        <v>0</v>
+      </c>
+      <c r="E24">
+        <v>946</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>37</v>
+      </c>
+      <c r="B25" t="s">
+        <v>38</v>
+      </c>
+      <c r="C25" t="s">
+        <v>36</v>
+      </c>
+      <c r="D25" s="2">
+        <v>0</v>
+      </c>
+      <c r="E25">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>39</v>
+      </c>
+      <c r="B26" t="s">
+        <v>38</v>
+      </c>
+      <c r="C26" t="s">
+        <v>36</v>
+      </c>
+      <c r="D26" s="2">
+        <v>0</v>
+      </c>
+      <c r="E26">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>40</v>
+      </c>
+      <c r="B27" t="s">
+        <v>38</v>
+      </c>
+      <c r="C27" t="s">
+        <v>36</v>
+      </c>
+      <c r="D27" s="2">
+        <v>0</v>
+      </c>
+      <c r="E27">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>41</v>
+      </c>
+      <c r="B28" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" s="2">
-        <v>0</v>
-      </c>
-      <c r="E3" s="2">
-        <v>1391000</v>
+      <c r="C28" t="s">
+        <v>42</v>
+      </c>
+      <c r="D28">
+        <v>548</v>
+      </c>
+      <c r="E28">
+        <v>1200000000</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>43</v>
+      </c>
+      <c r="B29" t="s">
+        <v>8</v>
+      </c>
+      <c r="C29" t="s">
+        <v>42</v>
+      </c>
+      <c r="D29" s="2">
+        <v>860</v>
+      </c>
+      <c r="E29">
+        <v>97000000</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>44</v>
+      </c>
+      <c r="B30" t="s">
+        <v>8</v>
+      </c>
+      <c r="C30" t="s">
+        <v>45</v>
+      </c>
+      <c r="D30" s="2">
+        <v>8.6</v>
+      </c>
+      <c r="E30">
+        <v>2392000</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>46</v>
+      </c>
+      <c r="B31" t="s">
+        <v>8</v>
+      </c>
+      <c r="C31" t="s">
+        <v>47</v>
+      </c>
+      <c r="D31" s="2">
+        <v>4.24</v>
+      </c>
+      <c r="E31">
+        <v>200000</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>48</v>
+      </c>
+      <c r="B32" t="s">
+        <v>8</v>
+      </c>
+      <c r="C32" t="s">
+        <v>47</v>
+      </c>
+      <c r="D32" s="2">
+        <v>4.37</v>
+      </c>
+      <c r="E32">
+        <v>1700000</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>49</v>
+      </c>
+      <c r="B33" t="s">
+        <v>8</v>
+      </c>
+      <c r="C33" t="s">
+        <v>47</v>
+      </c>
+      <c r="D33" s="2">
+        <v>4.37</v>
+      </c>
+      <c r="E33">
+        <v>1200000</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>50</v>
+      </c>
+      <c r="B34" t="s">
+        <v>8</v>
+      </c>
+      <c r="C34" t="s">
+        <v>51</v>
+      </c>
+      <c r="D34" s="2">
+        <v>25</v>
+      </c>
+      <c r="E34">
+        <v>2370000</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>52</v>
+      </c>
+      <c r="B35" t="s">
+        <v>8</v>
+      </c>
+      <c r="C35" t="s">
+        <v>53</v>
+      </c>
+      <c r="D35">
+        <v>16.7</v>
+      </c>
+      <c r="E35">
+        <v>1800000</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>54</v>
+      </c>
+      <c r="B36" t="s">
+        <v>8</v>
+      </c>
+      <c r="C36" t="s">
+        <v>55</v>
+      </c>
+      <c r="D36" s="2">
+        <v>2600</v>
+      </c>
+      <c r="E36">
+        <v>203000000</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>56</v>
+      </c>
+      <c r="B37" t="s">
+        <v>8</v>
+      </c>
+      <c r="C37" t="s">
+        <v>57</v>
+      </c>
+      <c r="D37">
+        <v>433</v>
+      </c>
+      <c r="E37">
+        <v>44000000</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>58</v>
+      </c>
+      <c r="B38" t="s">
+        <v>8</v>
+      </c>
+      <c r="C38" t="s">
+        <v>59</v>
+      </c>
+      <c r="D38" s="2">
+        <v>550</v>
+      </c>
+      <c r="E38">
+        <v>883000000</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>60</v>
+      </c>
+      <c r="B39" t="s">
+        <v>8</v>
+      </c>
+      <c r="C39" t="s">
+        <v>61</v>
+      </c>
+      <c r="D39">
+        <v>65</v>
+      </c>
+      <c r="E39">
+        <v>61000000</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>62</v>
+      </c>
+      <c r="B40" t="s">
+        <v>8</v>
+      </c>
+      <c r="C40" t="s">
+        <v>63</v>
+      </c>
+      <c r="D40" s="2">
+        <v>250</v>
+      </c>
+      <c r="E40">
+        <v>10500000</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>64</v>
+      </c>
+      <c r="B41" t="s">
+        <v>8</v>
+      </c>
+      <c r="C41" t="s">
+        <v>65</v>
+      </c>
+      <c r="D41">
+        <v>36.700000000000003</v>
+      </c>
+      <c r="E41">
+        <v>36000000</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>66</v>
+      </c>
+      <c r="B42" t="s">
+        <v>8</v>
+      </c>
+      <c r="C42" t="s">
+        <v>42</v>
+      </c>
+      <c r="D42" s="2">
+        <v>240</v>
+      </c>
+      <c r="E42">
+        <v>8400000</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>67</v>
+      </c>
+      <c r="B43" t="s">
+        <v>8</v>
+      </c>
+      <c r="C43" t="s">
+        <v>68</v>
+      </c>
+      <c r="D43">
+        <v>42.9</v>
+      </c>
+      <c r="E43">
+        <v>12000000</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>69</v>
+      </c>
+      <c r="B44" t="s">
+        <v>8</v>
+      </c>
+      <c r="C44" t="s">
+        <v>70</v>
+      </c>
+      <c r="D44" s="2">
+        <v>310</v>
+      </c>
+      <c r="E44">
+        <v>98000000</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>71</v>
+      </c>
+      <c r="B45" t="s">
+        <v>8</v>
+      </c>
+      <c r="C45" t="s">
+        <v>72</v>
+      </c>
+      <c r="D45">
+        <v>139</v>
+      </c>
+      <c r="E45">
+        <v>11000000</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>73</v>
+      </c>
+      <c r="B46" t="s">
+        <v>8</v>
+      </c>
+      <c r="C46" t="s">
+        <v>74</v>
+      </c>
+      <c r="D46" s="2">
+        <v>350</v>
+      </c>
+      <c r="E46">
+        <v>8400000</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>75</v>
+      </c>
+      <c r="B47" t="s">
+        <v>8</v>
+      </c>
+      <c r="C47" t="s">
+        <v>42</v>
+      </c>
+      <c r="D47">
+        <v>2000</v>
+      </c>
+      <c r="E47">
+        <v>74000000</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>76</v>
+      </c>
+      <c r="B48" t="s">
+        <v>8</v>
+      </c>
+      <c r="C48" t="s">
+        <v>42</v>
+      </c>
+      <c r="D48" s="2">
+        <v>1260</v>
+      </c>
+      <c r="E48">
+        <v>28000000</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>77</v>
+      </c>
+      <c r="B49" t="s">
+        <v>8</v>
+      </c>
+      <c r="C49" t="s">
+        <v>42</v>
+      </c>
+      <c r="D49">
+        <v>650</v>
+      </c>
+      <c r="E49">
+        <v>22000000</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>78</v>
+      </c>
+      <c r="B50" t="s">
+        <v>8</v>
+      </c>
+      <c r="C50" t="s">
+        <v>79</v>
+      </c>
+      <c r="D50" s="2">
+        <v>5.96</v>
+      </c>
+      <c r="E50">
+        <v>280000</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>80</v>
+      </c>
+      <c r="B51" t="s">
+        <v>8</v>
+      </c>
+      <c r="C51" t="s">
+        <v>81</v>
+      </c>
+      <c r="D51">
+        <v>40</v>
+      </c>
+      <c r="E51">
+        <v>167000</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>82</v>
+      </c>
+      <c r="B52" t="s">
+        <v>84</v>
+      </c>
+      <c r="C52" t="s">
+        <v>55</v>
+      </c>
+      <c r="D52" s="2">
+        <v>600</v>
+      </c>
+      <c r="E52">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>83</v>
+      </c>
+      <c r="B53" t="s">
+        <v>84</v>
+      </c>
+      <c r="C53" t="s">
+        <v>55</v>
+      </c>
+      <c r="D53">
+        <v>1400</v>
+      </c>
+      <c r="E53">
+        <v>32000</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>86</v>
+      </c>
+      <c r="B54" t="s">
+        <v>84</v>
+      </c>
+      <c r="C54" t="s">
+        <v>85</v>
+      </c>
+      <c r="D54" s="2">
+        <v>159</v>
+      </c>
+      <c r="E54">
+        <v>143000</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>87</v>
+      </c>
+      <c r="B55" t="s">
+        <v>84</v>
+      </c>
+      <c r="C55" t="s">
+        <v>85</v>
+      </c>
+      <c r="D55">
+        <v>50</v>
+      </c>
+      <c r="E55">
+        <v>200000</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>88</v>
+      </c>
+      <c r="B56" t="s">
+        <v>84</v>
+      </c>
+      <c r="C56" t="s">
+        <v>68</v>
+      </c>
+      <c r="D56" s="2">
+        <v>1400</v>
+      </c>
+      <c r="E56">
+        <v>250000</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>89</v>
+      </c>
+      <c r="B57" t="s">
+        <v>90</v>
+      </c>
+      <c r="C57" t="s">
+        <v>91</v>
+      </c>
+      <c r="D57">
+        <v>2537000</v>
+      </c>
+      <c r="E57">
+        <v>220000</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>92</v>
+      </c>
+      <c r="B58" t="s">
+        <v>90</v>
+      </c>
+      <c r="C58" t="s">
+        <v>91</v>
+      </c>
+      <c r="D58" s="2">
+        <v>0</v>
+      </c>
+      <c r="E58">
+        <v>105700</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>93</v>
+      </c>
+      <c r="B59" t="s">
+        <v>90</v>
+      </c>
+      <c r="C59" t="s">
+        <v>91</v>
+      </c>
+      <c r="D59">
+        <v>3000000</v>
+      </c>
+      <c r="E59">
+        <v>60000</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>94</v>
+      </c>
+      <c r="B60" t="s">
+        <v>90</v>
+      </c>
+      <c r="C60" t="s">
+        <v>63</v>
+      </c>
+      <c r="D60" s="2">
+        <v>53000000</v>
+      </c>
+      <c r="E60">
+        <v>240000</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>95</v>
+      </c>
+      <c r="B61" t="s">
+        <v>90</v>
+      </c>
+      <c r="C61" t="s">
+        <v>63</v>
+      </c>
+      <c r="D61">
+        <v>29000000</v>
+      </c>
+      <c r="E61">
+        <v>49000</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>96</v>
+      </c>
+      <c r="B62" t="s">
+        <v>90</v>
+      </c>
+      <c r="C62" t="s">
+        <v>97</v>
+      </c>
+      <c r="D62">
+        <v>23000000</v>
+      </c>
+      <c r="E62">
+        <v>76000</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>98</v>
+      </c>
+      <c r="B63" t="s">
+        <v>90</v>
+      </c>
+      <c r="C63" t="s">
+        <v>72</v>
+      </c>
+      <c r="D63" s="3">
+        <v>61000000</v>
+      </c>
+      <c r="E63">
+        <v>110000</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>99</v>
+      </c>
+      <c r="B64" t="s">
+        <v>90</v>
+      </c>
+      <c r="C64" t="s">
+        <v>101</v>
+      </c>
+      <c r="D64">
+        <v>12000000</v>
+      </c>
+      <c r="E64">
+        <v>90000</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>100</v>
+      </c>
+      <c r="B65" t="s">
+        <v>90</v>
+      </c>
+      <c r="C65" t="s">
+        <v>101</v>
+      </c>
+      <c r="D65">
+        <v>12000000</v>
+      </c>
+      <c r="E65">
+        <v>37000</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>102</v>
+      </c>
+      <c r="B66" t="s">
+        <v>90</v>
+      </c>
+      <c r="C66" t="s">
+        <v>104</v>
+      </c>
+      <c r="D66">
+        <v>163000</v>
+      </c>
+      <c r="E66">
+        <v>14000</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>103</v>
+      </c>
+      <c r="B67" t="s">
+        <v>90</v>
+      </c>
+      <c r="C67" t="s">
+        <v>104</v>
+      </c>
+      <c r="D67">
+        <v>200000</v>
+      </c>
+      <c r="E67">
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>105</v>
+      </c>
+      <c r="B68" t="s">
+        <v>106</v>
+      </c>
+      <c r="C68" t="s">
+        <v>42</v>
+      </c>
+      <c r="D68">
+        <v>1344</v>
+      </c>
+      <c r="E68">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>107</v>
+      </c>
+      <c r="B69" t="s">
+        <v>106</v>
+      </c>
+      <c r="C69" t="s">
+        <v>81</v>
+      </c>
+      <c r="D69">
+        <v>650</v>
+      </c>
+      <c r="E69">
+        <v>2.87</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>108</v>
+      </c>
+      <c r="B70" t="s">
+        <v>106</v>
+      </c>
+      <c r="C70" t="s">
+        <v>70</v>
+      </c>
+      <c r="D70">
+        <v>7500</v>
+      </c>
+      <c r="E70">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>109</v>
+      </c>
+      <c r="B71" t="s">
+        <v>106</v>
+      </c>
+      <c r="C71" t="s">
+        <v>115</v>
+      </c>
+      <c r="D71">
+        <v>7000</v>
+      </c>
+      <c r="E71">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>110</v>
+      </c>
+      <c r="B72" t="s">
+        <v>106</v>
+      </c>
+      <c r="C72" t="s">
+        <v>116</v>
+      </c>
+      <c r="D72">
+        <v>4100</v>
+      </c>
+      <c r="E72">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>111</v>
+      </c>
+      <c r="B73" t="s">
+        <v>106</v>
+      </c>
+      <c r="C73" t="s">
+        <v>116</v>
+      </c>
+      <c r="D73">
+        <v>5200</v>
+      </c>
+      <c r="E73">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>112</v>
+      </c>
+      <c r="B74" t="s">
+        <v>106</v>
+      </c>
+      <c r="C74" t="s">
+        <v>117</v>
+      </c>
+      <c r="D74">
+        <v>5200</v>
+      </c>
+      <c r="E74">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>113</v>
+      </c>
+      <c r="B75" t="s">
+        <v>106</v>
+      </c>
+      <c r="C75" t="s">
+        <v>61</v>
+      </c>
+      <c r="D75">
+        <v>6500</v>
+      </c>
+      <c r="E75">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>114</v>
+      </c>
+      <c r="B76" t="s">
+        <v>106</v>
+      </c>
+      <c r="C76" t="s">
+        <v>118</v>
+      </c>
+      <c r="D76">
+        <v>3300</v>
+      </c>
+      <c r="E76">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>119</v>
+      </c>
+      <c r="B77" t="s">
+        <v>120</v>
+      </c>
+      <c r="C77" t="s">
+        <v>121</v>
+      </c>
+      <c r="D77">
+        <v>26000</v>
+      </c>
+      <c r="E77">
+        <v>44000000</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>122</v>
+      </c>
+      <c r="B78" t="s">
+        <v>120</v>
+      </c>
+      <c r="C78" t="s">
+        <v>97</v>
+      </c>
+      <c r="D78">
+        <v>10400000000</v>
+      </c>
+      <c r="E78">
+        <v>390000000000</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>123</v>
+      </c>
+      <c r="B79" t="s">
+        <v>120</v>
+      </c>
+      <c r="C79" t="s">
+        <v>55</v>
+      </c>
+      <c r="D79">
+        <v>6070</v>
+      </c>
+      <c r="E79">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>124</v>
+      </c>
+      <c r="B80" t="s">
+        <v>120</v>
+      </c>
+      <c r="C80" t="s">
+        <v>117</v>
+      </c>
+      <c r="D80">
+        <v>3000</v>
+      </c>
+      <c r="E80">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>125</v>
+      </c>
+      <c r="B81" t="s">
+        <v>126</v>
+      </c>
+      <c r="C81" t="s">
+        <v>127</v>
+      </c>
+      <c r="D81">
+        <v>0</v>
+      </c>
+      <c r="E81">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>128</v>
+      </c>
+      <c r="B82" t="s">
+        <v>126</v>
+      </c>
+      <c r="C82" t="s">
+        <v>127</v>
+      </c>
+      <c r="D82">
+        <v>0</v>
+      </c>
+      <c r="E82">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>129</v>
+      </c>
+      <c r="B83" t="s">
+        <v>126</v>
+      </c>
+      <c r="C83" t="s">
+        <v>127</v>
+      </c>
+      <c r="D83">
+        <v>0</v>
+      </c>
+      <c r="E83">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>130</v>
+      </c>
+      <c r="B84" t="s">
+        <v>38</v>
+      </c>
+      <c r="C84" t="s">
+        <v>36</v>
+      </c>
+      <c r="D84">
+        <v>0</v>
+      </c>
+      <c r="E84">
+        <v>0.49</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>131</v>
+      </c>
+      <c r="B85" t="s">
+        <v>38</v>
+      </c>
+      <c r="C85" t="s">
+        <v>132</v>
+      </c>
+      <c r="D85">
+        <v>0</v>
+      </c>
+      <c r="E85">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>133</v>
+      </c>
+      <c r="B86" t="s">
+        <v>38</v>
+      </c>
+      <c r="C86" t="s">
+        <v>132</v>
+      </c>
+      <c r="D86">
+        <v>0</v>
+      </c>
+      <c r="E86">
+        <v>16.8</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>134</v>
+      </c>
+      <c r="B87" t="s">
+        <v>38</v>
+      </c>
+      <c r="C87" t="s">
+        <v>132</v>
+      </c>
+      <c r="D87">
+        <v>0</v>
+      </c>
+      <c r="E87">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>135</v>
+      </c>
+      <c r="B88" t="s">
+        <v>38</v>
+      </c>
+      <c r="C88" t="s">
+        <v>132</v>
+      </c>
+      <c r="D88">
+        <v>0</v>
+      </c>
+      <c r="E88">
+        <v>0.87</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>136</v>
+      </c>
+      <c r="B89" t="s">
+        <v>17</v>
+      </c>
+      <c r="C89" t="s">
+        <v>28</v>
+      </c>
+      <c r="D89">
+        <v>0</v>
+      </c>
+      <c r="E89">
+        <v>1212</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>137</v>
+      </c>
+      <c r="B90" t="s">
+        <v>17</v>
+      </c>
+      <c r="C90" t="s">
+        <v>15</v>
+      </c>
+      <c r="D90">
+        <v>0</v>
+      </c>
+      <c r="E90">
+        <v>2706</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>138</v>
+      </c>
+      <c r="B91" t="s">
+        <v>17</v>
+      </c>
+      <c r="C91" t="s">
+        <v>14</v>
+      </c>
+      <c r="D91">
+        <v>0</v>
+      </c>
+      <c r="E91">
+        <v>1523</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>139</v>
+      </c>
+      <c r="B92" t="s">
+        <v>17</v>
+      </c>
+      <c r="C92" t="s">
+        <v>14</v>
+      </c>
+      <c r="D92">
+        <v>0</v>
+      </c>
+      <c r="E92">
+        <v>1578</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>140</v>
+      </c>
+      <c r="B93" t="s">
+        <v>17</v>
+      </c>
+      <c r="C93" t="s">
+        <v>14</v>
+      </c>
+      <c r="D93">
+        <v>0</v>
+      </c>
+      <c r="E93">
+        <v>1169</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>141</v>
+      </c>
+      <c r="B94" t="s">
+        <v>17</v>
+      </c>
+      <c r="C94" t="s">
+        <v>14</v>
+      </c>
+      <c r="D94">
+        <v>0</v>
+      </c>
+      <c r="E94">
+        <v>1158</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>142</v>
+      </c>
+      <c r="B95" t="s">
+        <v>17</v>
+      </c>
+      <c r="C95" t="s">
+        <v>14</v>
+      </c>
+      <c r="D95">
+        <v>0</v>
+      </c>
+      <c r="E95">
+        <v>1169</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>143</v>
+      </c>
+      <c r="B96" t="s">
+        <v>17</v>
+      </c>
+      <c r="C96" t="s">
+        <v>13</v>
+      </c>
+      <c r="D96">
+        <v>0</v>
+      </c>
+      <c r="E96">
+        <v>1528</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>144</v>
+      </c>
+      <c r="B97" t="s">
+        <v>17</v>
+      </c>
+      <c r="C97" t="s">
+        <v>13</v>
+      </c>
+      <c r="D97">
+        <v>0</v>
+      </c>
+      <c r="E97">
+        <v>1123</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>145</v>
+      </c>
+      <c r="B98" t="s">
+        <v>17</v>
+      </c>
+      <c r="C98" t="s">
+        <v>13</v>
+      </c>
+      <c r="D98">
+        <v>0</v>
+      </c>
+      <c r="E98">
+        <v>1062</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>146</v>
+      </c>
+      <c r="B99" t="s">
+        <v>17</v>
+      </c>
+      <c r="C99" t="s">
+        <v>13</v>
+      </c>
+      <c r="D99">
+        <v>0</v>
+      </c>
+      <c r="E99">
+        <v>1469</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>147</v>
+      </c>
+      <c r="B100" t="s">
+        <v>17</v>
+      </c>
+      <c r="C100" t="s">
+        <v>13</v>
+      </c>
+      <c r="D100">
+        <v>0</v>
+      </c>
+      <c r="E100">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>148</v>
+      </c>
+      <c r="B101" t="s">
+        <v>17</v>
+      </c>
+      <c r="C101" t="s">
+        <v>13</v>
+      </c>
+      <c r="D101">
+        <v>0</v>
+      </c>
+      <c r="E101">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>149</v>
+      </c>
+      <c r="B102" t="s">
+        <v>17</v>
+      </c>
+      <c r="C102" t="s">
+        <v>15</v>
+      </c>
+      <c r="D102">
+        <v>0</v>
+      </c>
+      <c r="E102">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>150</v>
+      </c>
+      <c r="B103" t="s">
+        <v>17</v>
+      </c>
+      <c r="C103" t="s">
+        <v>15</v>
+      </c>
+      <c r="D103">
+        <v>0</v>
+      </c>
+      <c r="E103">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>151</v>
+      </c>
+      <c r="B104" t="s">
+        <v>17</v>
+      </c>
+      <c r="C104" t="s">
+        <v>15</v>
+      </c>
+      <c r="D104">
+        <v>0</v>
+      </c>
+      <c r="E104">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>152</v>
+      </c>
+      <c r="B105" t="s">
+        <v>17</v>
+      </c>
+      <c r="C105" t="s">
+        <v>15</v>
+      </c>
+      <c r="D105">
+        <v>0</v>
+      </c>
+      <c r="E105">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>153</v>
+      </c>
+      <c r="B106" t="s">
+        <v>17</v>
+      </c>
+      <c r="C106" t="s">
+        <v>15</v>
+      </c>
+      <c r="D106">
+        <v>0</v>
+      </c>
+      <c r="E106">
+        <v>174</v>
       </c>
     </row>
   </sheetData>
